--- a/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
+++ b/public/contoh_excel/TEMPLATE MENU UPLOAD TAGIHAN EXCEL.xlsx
@@ -47,13 +47,13 @@
     <t>NOMINAL</t>
   </si>
   <si>
-    <t>ICT TES 3</t>
+    <t>FULAN 1</t>
   </si>
   <si>
     <t>SD</t>
   </si>
   <si>
-    <t>B</t>
+    <t>C</t>
   </si>
   <si>
     <t>2026/2027</t>
@@ -62,7 +62,7 @@
     <t>L</t>
   </si>
   <si>
-    <t>Serang</t>
+    <t>Semarang</t>
   </si>
   <si>
     <t>Gatot</t>
@@ -436,13 +436,13 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="11.569" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -481,7 +481,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2">
-        <v>880090</v>
+        <v>770078</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
